--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -498,7 +498,35 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -831,18 +859,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18.25" customWidth="1"/>
     <col min="4" max="4" width="16.875" customWidth="1"/>
-    <col min="5" max="5" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="12.125" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -851,7 +879,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -867,8 +895,12 @@
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="8">
+        <f>C115</f>
+        <v>2258000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <f xml:space="preserve"> F3</f>
         <v>130000</v>
@@ -888,7 +920,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <f t="shared" ref="A4:A15" si="0" xml:space="preserve"> A3 + F4</f>
         <v>155000</v>
@@ -908,7 +940,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>313000</v>
@@ -928,7 +960,7 @@
         <v>158000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>463000</v>
@@ -948,7 +980,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>524000</v>
@@ -968,7 +1000,7 @@
         <v>61000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -988,7 +1020,7 @@
         <v>-524000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>180000</v>
@@ -1008,7 +1040,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>270000</v>
@@ -1028,7 +1060,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>170000</v>
@@ -1048,7 +1080,7 @@
         <v>-100000</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>280000</v>
@@ -1068,7 +1100,7 @@
         <v>110000</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1088,7 +1120,7 @@
         <v>-280000</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <f t="shared" si="0"/>
         <v>225000</v>
@@ -1108,7 +1140,7 @@
         <v>225000</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <f t="shared" si="0"/>
         <v>363000</v>
@@ -1128,7 +1160,7 @@
         <v>138000</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="8">
         <f xml:space="preserve"> B3 + B4 + B5 + B6 + B7 + B8 + B9 +B10 + B11 + B12 + B13 + B14 + B15</f>
@@ -2290,44 +2322,265 @@
       </c>
     </row>
     <row r="90" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" s="10"/>
+    </row>
+    <row r="92" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="7">
+        <f xml:space="preserve"> C89+B93-C93</f>
+        <v>2258000</v>
+      </c>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+    </row>
+    <row r="94" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="7">
+        <f xml:space="preserve"> A93 +B94-C94</f>
+        <v>2258000</v>
+      </c>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+    </row>
+    <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="7">
+        <f t="shared" ref="A95:A111" si="7" xml:space="preserve"> A94 +B95-C95</f>
+        <v>2258000</v>
+      </c>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+    </row>
+    <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+    </row>
+    <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+    </row>
+    <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+    </row>
+    <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+    </row>
+    <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+    </row>
+    <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+    </row>
+    <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+    </row>
+    <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+    </row>
+    <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+    </row>
+    <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+    </row>
+    <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+    </row>
+    <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+    </row>
+    <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+    </row>
+    <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+    </row>
+    <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+    </row>
+    <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="7">
+        <f t="shared" si="7"/>
+        <v>2258000</v>
+      </c>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+    </row>
+    <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="7">
+        <f xml:space="preserve"> A111 +B112-C112</f>
+        <v>2258000</v>
+      </c>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="8">
+        <f>SUM(B93:B112)+B87</f>
+        <v>13710000</v>
+      </c>
+      <c r="C113" s="8">
+        <f>SUM(C93:C112)+C87</f>
+        <v>11452000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C115" s="13">
+        <f>A112</f>
+        <v>2258000</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="129" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="130" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="131" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2351,20 +2604,34 @@
     <row r="149" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="C62">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C89">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C115">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
-        <f xml:space="preserve"> F3</f>
+        <f xml:space="preserve"> B3</f>
         <v>130000</v>
       </c>
       <c r="B3" s="7">
@@ -915,14 +915,10 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3">
-        <f>B3 - C3</f>
-        <v>130000</v>
-      </c>
     </row>
     <row r="4" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
-        <f t="shared" ref="A4:A15" si="0" xml:space="preserve"> A3 + F4</f>
+        <f xml:space="preserve"> A3 + B4-C4</f>
         <v>155000</v>
       </c>
       <c r="B4" s="7">
@@ -935,14 +931,10 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4">
-        <f t="shared" ref="F4:F15" si="1" xml:space="preserve"> B4 - C4</f>
-        <v>25000</v>
-      </c>
     </row>
     <row r="5" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A5:A15" si="0" xml:space="preserve"> A4 + B5-C5</f>
         <v>313000</v>
       </c>
       <c r="B5" s="7">
@@ -954,10 +946,6 @@
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="1"/>
-        <v>158000</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -975,10 +963,6 @@
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>150000</v>
-      </c>
     </row>
     <row r="7" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
@@ -995,10 +979,6 @@
       <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F7">
-        <f t="shared" si="1"/>
-        <v>61000</v>
-      </c>
     </row>
     <row r="8" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
@@ -1015,10 +995,6 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8">
-        <f t="shared" si="1"/>
-        <v>-524000</v>
-      </c>
     </row>
     <row r="9" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
@@ -1035,10 +1011,6 @@
       <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="1"/>
-        <v>180000</v>
-      </c>
     </row>
     <row r="10" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
@@ -1055,10 +1027,6 @@
       <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10">
-        <f t="shared" si="1"/>
-        <v>90000</v>
-      </c>
     </row>
     <row r="11" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
@@ -1075,10 +1043,6 @@
       <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="1"/>
-        <v>-100000</v>
-      </c>
     </row>
     <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
@@ -1095,10 +1059,6 @@
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F12">
-        <f t="shared" si="1"/>
-        <v>110000</v>
-      </c>
     </row>
     <row r="13" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
@@ -1115,10 +1075,6 @@
       <c r="E13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="1"/>
-        <v>-280000</v>
-      </c>
     </row>
     <row r="14" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
@@ -1135,14 +1091,10 @@
       <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="1"/>
-        <v>225000</v>
-      </c>
     </row>
     <row r="15" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
-        <f t="shared" si="0"/>
+        <f xml:space="preserve"> A14 + B15-C15</f>
         <v>363000</v>
       </c>
       <c r="B15" s="7">
@@ -1154,10 +1106,6 @@
       </c>
       <c r="E15" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>138000</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1171,7 +1119,7 @@
         <v>904000</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8">
@@ -1185,7 +1133,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>6</v>
       </c>
@@ -1195,19 +1143,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="10" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="10"/>
     </row>
-    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>4</v>
       </c>
@@ -1224,10 +1172,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
-        <f xml:space="preserve"> F22</f>
-        <v>696000</v>
+        <f xml:space="preserve"> C17</f>
+        <v>363000</v>
       </c>
       <c r="B22" s="7">
         <v>333000</v>
@@ -1239,15 +1187,11 @@
       <c r="E22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="8">
-        <f>B22 + C17 - C22</f>
-        <v>696000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
-        <f t="shared" ref="A23:A34" si="2" xml:space="preserve"> A22 + F23</f>
-        <v>894000</v>
+        <f xml:space="preserve"> A22 + B23-C23</f>
+        <v>561000</v>
       </c>
       <c r="B23" s="7">
         <v>198000</v>
@@ -1259,15 +1203,11 @@
       <c r="E23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F23">
-        <f t="shared" ref="F23:F34" si="3" xml:space="preserve"> B23 - C23</f>
-        <v>198000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
-        <f t="shared" si="2"/>
-        <v>1123000</v>
+        <f t="shared" ref="A24:A34" si="1" xml:space="preserve"> A23 + B24-C24</f>
+        <v>790000</v>
       </c>
       <c r="B24" s="7">
         <v>229000</v>
@@ -1279,15 +1219,11 @@
       <c r="E24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F24">
-        <f t="shared" si="3"/>
-        <v>229000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
-        <f t="shared" si="2"/>
-        <v>1419000</v>
+        <f t="shared" si="1"/>
+        <v>1086000</v>
       </c>
       <c r="B25" s="7">
         <v>296000</v>
@@ -1299,15 +1235,11 @@
       <c r="E25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F25">
-        <f t="shared" si="3"/>
-        <v>296000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
-        <f t="shared" si="2"/>
-        <v>1484000</v>
+        <f t="shared" si="1"/>
+        <v>1151000</v>
       </c>
       <c r="B26" s="7">
         <v>65000</v>
@@ -1319,15 +1251,11 @@
       <c r="E26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F26">
-        <f t="shared" si="3"/>
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
-        <f t="shared" si="2"/>
-        <v>1697000</v>
+        <f t="shared" si="1"/>
+        <v>1364000</v>
       </c>
       <c r="B27" s="7">
         <v>213000</v>
@@ -1339,15 +1267,11 @@
       <c r="E27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F27">
-        <f t="shared" si="3"/>
-        <v>213000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
-        <f t="shared" si="2"/>
-        <v>1746000</v>
+        <f t="shared" si="1"/>
+        <v>1413000</v>
       </c>
       <c r="B28" s="7">
         <v>49000</v>
@@ -1359,15 +1283,11 @@
       <c r="E28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F28">
-        <f t="shared" si="3"/>
-        <v>49000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>-333000</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7">
@@ -1379,15 +1299,11 @@
       <c r="E29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F29">
-        <f t="shared" si="3"/>
-        <v>-1746000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
-        <f t="shared" si="2"/>
-        <v>185000</v>
+        <f t="shared" si="1"/>
+        <v>-148000</v>
       </c>
       <c r="B30" s="7">
         <v>185000</v>
@@ -1399,15 +1315,11 @@
       <c r="E30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F30">
-        <f t="shared" si="3"/>
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
-        <f t="shared" si="2"/>
-        <v>270000</v>
+        <f t="shared" si="1"/>
+        <v>-63000</v>
       </c>
       <c r="B31" s="7">
         <v>85000</v>
@@ -1419,15 +1331,11 @@
       <c r="E31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F31">
-        <f t="shared" si="3"/>
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
-        <f t="shared" si="2"/>
-        <v>470000</v>
+        <f t="shared" si="1"/>
+        <v>137000</v>
       </c>
       <c r="B32" s="7">
         <v>200000</v>
@@ -1439,15 +1347,11 @@
       <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F32">
-        <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
-        <f t="shared" si="2"/>
-        <v>585000</v>
+        <f t="shared" si="1"/>
+        <v>252000</v>
       </c>
       <c r="B33" s="7">
         <v>115000</v>
@@ -1459,15 +1363,11 @@
       <c r="E33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F33">
-        <f t="shared" si="3"/>
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
+        <f t="shared" si="1"/>
+        <v>667000</v>
       </c>
       <c r="B34" s="7">
         <v>415000</v>
@@ -1479,12 +1379,8 @@
       <c r="E34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F34">
-        <f t="shared" si="3"/>
-        <v>415000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="8">
         <f xml:space="preserve"> B22 + B23 + B24 + B25 + B26 + B27 + B28 +B29 + B30 + B31 + B32 + B33 + B34 +B16</f>
@@ -1495,12 +1391,12 @@
         <v>2650000</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="13">
         <f xml:space="preserve"> A34</f>
-        <v>1000000</v>
+        <v>667000</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>8</v>
@@ -1509,7 +1405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>6</v>
       </c>
@@ -1517,7 +1413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>14</v>
       </c>
@@ -1526,7 +1422,7 @@
       </c>
       <c r="C38" s="10"/>
     </row>
-    <row r="39" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
         <v>4</v>
       </c>
@@ -1543,10 +1439,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
-        <f xml:space="preserve"> F40</f>
-        <v>0</v>
+        <f xml:space="preserve"> C36-C40</f>
+        <v>-333000</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7">
@@ -1558,15 +1454,11 @@
       <c r="E40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="8">
-        <f>B40 + C36 - C40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
-        <f t="shared" ref="A41:A59" si="4" xml:space="preserve"> A40 + F41</f>
-        <v>360000</v>
+        <f xml:space="preserve"> A40 + B41-C41</f>
+        <v>27000</v>
       </c>
       <c r="B41" s="7">
         <v>360000</v>
@@ -1578,15 +1470,11 @@
       <c r="E41" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F41">
-        <f t="shared" ref="F41:F59" si="5" xml:space="preserve"> B41 - C41</f>
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
-        <f t="shared" si="4"/>
-        <v>506000</v>
+        <f t="shared" ref="A42:A59" si="2" xml:space="preserve"> A41 + B42-C42</f>
+        <v>173000</v>
       </c>
       <c r="B42" s="7">
         <v>146000</v>
@@ -1598,15 +1486,11 @@
       <c r="E42" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F42">
-        <f t="shared" si="5"/>
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
-        <f t="shared" si="4"/>
-        <v>626000</v>
+        <f t="shared" si="2"/>
+        <v>293000</v>
       </c>
       <c r="B43" s="7">
         <v>120000</v>
@@ -1618,15 +1502,11 @@
       <c r="E43" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F43">
-        <f t="shared" si="5"/>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
-        <f t="shared" si="4"/>
-        <v>760000</v>
+        <f t="shared" si="2"/>
+        <v>427000</v>
       </c>
       <c r="B44" s="7">
         <v>134000</v>
@@ -1638,15 +1518,11 @@
       <c r="E44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F44">
-        <f t="shared" si="5"/>
-        <v>134000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
-        <f t="shared" si="4"/>
-        <v>1137000</v>
+        <f t="shared" si="2"/>
+        <v>804000</v>
       </c>
       <c r="B45" s="7">
         <v>377000</v>
@@ -1658,15 +1534,11 @@
       <c r="E45" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F45">
-        <f t="shared" si="5"/>
-        <v>377000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
-        <f t="shared" si="4"/>
-        <v>1414000</v>
+        <f t="shared" si="2"/>
+        <v>1081000</v>
       </c>
       <c r="B46" s="7">
         <v>277000</v>
@@ -1678,15 +1550,11 @@
       <c r="E46" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F46">
-        <f t="shared" si="5"/>
-        <v>277000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
-        <f t="shared" si="4"/>
-        <v>1659000</v>
+        <f t="shared" si="2"/>
+        <v>1326000</v>
       </c>
       <c r="B47" s="7">
         <v>245000</v>
@@ -1698,15 +1566,11 @@
       <c r="E47" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F47">
-        <f t="shared" si="5"/>
-        <v>245000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
-        <f t="shared" si="4"/>
-        <v>1774000</v>
+        <f t="shared" si="2"/>
+        <v>1441000</v>
       </c>
       <c r="B48" s="7">
         <v>115000</v>
@@ -1718,15 +1582,11 @@
       <c r="E48" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F48">
-        <f t="shared" si="5"/>
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>-333000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7">
@@ -1738,15 +1598,11 @@
       <c r="E49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F49">
-        <f t="shared" si="5"/>
-        <v>-1774000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
-        <f t="shared" si="4"/>
-        <v>346000</v>
+        <f t="shared" si="2"/>
+        <v>13000</v>
       </c>
       <c r="B50" s="7">
         <v>346000</v>
@@ -1758,15 +1614,11 @@
       <c r="E50" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F50">
-        <f t="shared" si="5"/>
-        <v>346000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
-        <f t="shared" si="4"/>
-        <v>1104000</v>
+        <f t="shared" si="2"/>
+        <v>771000</v>
       </c>
       <c r="B51" s="7">
         <v>758000</v>
@@ -1778,15 +1630,11 @@
       <c r="E51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F51">
-        <f t="shared" si="5"/>
-        <v>758000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
-        <f t="shared" si="4"/>
-        <v>1641000</v>
+        <f t="shared" si="2"/>
+        <v>1308000</v>
       </c>
       <c r="B52" s="7">
         <v>537000</v>
@@ -1798,15 +1646,11 @@
       <c r="E52" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F52">
-        <f t="shared" si="5"/>
-        <v>537000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
-        <f t="shared" si="4"/>
-        <v>1701000</v>
+        <f t="shared" si="2"/>
+        <v>1368000</v>
       </c>
       <c r="B53" s="7">
         <v>60000</v>
@@ -1818,15 +1662,11 @@
       <c r="E53" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F53">
-        <f t="shared" si="5"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
-        <f t="shared" si="4"/>
-        <v>701000</v>
+        <f t="shared" si="2"/>
+        <v>368000</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="15">
@@ -1836,15 +1676,11 @@
         <v>50</v>
       </c>
       <c r="E54" s="14"/>
-      <c r="F54">
-        <f t="shared" si="5"/>
-        <v>-1000000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
-        <f t="shared" si="4"/>
-        <v>821000</v>
+        <f t="shared" si="2"/>
+        <v>488000</v>
       </c>
       <c r="B55" s="1">
         <v>120000</v>
@@ -1856,15 +1692,11 @@
       <c r="E55" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F55">
-        <f t="shared" si="5"/>
-        <v>120000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
-        <f t="shared" si="4"/>
-        <v>911000</v>
+        <f t="shared" si="2"/>
+        <v>578000</v>
       </c>
       <c r="B56" s="1">
         <v>90000</v>
@@ -1876,15 +1708,11 @@
       <c r="E56" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F56">
-        <f t="shared" si="5"/>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
-        <f t="shared" si="4"/>
-        <v>1300000</v>
+        <f t="shared" si="2"/>
+        <v>967000</v>
       </c>
       <c r="B57" s="1">
         <v>389000</v>
@@ -1896,15 +1724,11 @@
       <c r="E57" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F57">
-        <f t="shared" si="5"/>
-        <v>389000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
-        <f t="shared" si="4"/>
-        <v>1748000</v>
+        <f t="shared" si="2"/>
+        <v>1415000</v>
       </c>
       <c r="B58" s="1">
         <v>448000</v>
@@ -1916,15 +1740,11 @@
       <c r="E58" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F58">
-        <f t="shared" si="5"/>
-        <v>448000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
-        <f t="shared" si="4"/>
-        <v>1913000</v>
+        <f t="shared" si="2"/>
+        <v>1580000</v>
       </c>
       <c r="B59" s="1">
         <v>165000</v>
@@ -1936,12 +1756,8 @@
       <c r="E59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F59">
-        <f t="shared" si="5"/>
-        <v>165000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="8">
         <f>SUM(B40:B59)+B35</f>
         <v>8337000</v>
@@ -1951,18 +1767,18 @@
         <v>6424000</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C62" s="13">
         <f>A59</f>
-        <v>1913000</v>
+        <v>1580000</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>14</v>
@@ -1992,7 +1808,7 @@
     <row r="67" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <f xml:space="preserve"> C62+B67-C67</f>
-        <v>1963000</v>
+        <v>1630000</v>
       </c>
       <c r="B67" s="7">
         <v>50000</v>
@@ -2012,7 +1828,7 @@
       </c>
       <c r="B68" s="7"/>
       <c r="C68" s="7">
-        <v>1963000</v>
+        <v>1630000</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>50</v>
@@ -2023,7 +1839,7 @@
     </row>
     <row r="69" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
-        <f t="shared" ref="A69:A85" si="6" xml:space="preserve"> A68 +B69-C69</f>
+        <f t="shared" ref="A69:A85" si="3" xml:space="preserve"> A68 +B69-C69</f>
         <v>222000</v>
       </c>
       <c r="B69" s="7">
@@ -2039,7 +1855,7 @@
     </row>
     <row r="70" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="B70" s="7"/>
@@ -2055,7 +1871,7 @@
     </row>
     <row r="71" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>319000</v>
       </c>
       <c r="B71" s="7">
@@ -2071,7 +1887,7 @@
     </row>
     <row r="72" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>643000</v>
       </c>
       <c r="B72" s="7">
@@ -2087,7 +1903,7 @@
     </row>
     <row r="73" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1079000</v>
       </c>
       <c r="B73" s="7">
@@ -2103,7 +1919,7 @@
     </row>
     <row r="74" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1654000</v>
       </c>
       <c r="B74" s="7">
@@ -2119,7 +1935,7 @@
     </row>
     <row r="75" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2166000</v>
       </c>
       <c r="B75" s="7">
@@ -2135,7 +1951,7 @@
     </row>
     <row r="76" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2715000</v>
       </c>
       <c r="B76" s="7">
@@ -2151,7 +1967,7 @@
     </row>
     <row r="77" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2845000</v>
       </c>
       <c r="B77" s="7">
@@ -2165,7 +1981,7 @@
     </row>
     <row r="78" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="B78" s="7"/>
@@ -2181,7 +1997,7 @@
     </row>
     <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>190000</v>
       </c>
       <c r="B79" s="7">
@@ -2197,7 +2013,7 @@
     </row>
     <row r="80" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>874000</v>
       </c>
       <c r="B80" s="7">
@@ -2213,7 +2029,7 @@
     </row>
     <row r="81" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>954000</v>
       </c>
       <c r="B81" s="7">
@@ -2227,7 +2043,7 @@
     </row>
     <row r="82" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1232000</v>
       </c>
       <c r="B82" s="1">
@@ -2243,7 +2059,7 @@
     </row>
     <row r="83" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1400000</v>
       </c>
       <c r="B83" s="1">
@@ -2259,7 +2075,7 @@
     </row>
     <row r="84" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>1943000</v>
       </c>
       <c r="B84" s="1">
@@ -2275,7 +2091,7 @@
     </row>
     <row r="85" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2113000</v>
       </c>
       <c r="B85" s="1">
@@ -2308,7 +2124,7 @@
       </c>
       <c r="C87" s="8">
         <f>SUM(C67:C86)+C60</f>
-        <v>11452000</v>
+        <v>11119000</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2370,7 +2186,7 @@
     </row>
     <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
-        <f t="shared" ref="A95:A111" si="7" xml:space="preserve"> A94 +B95-C95</f>
+        <f t="shared" ref="A95:A111" si="4" xml:space="preserve"> A94 +B95-C95</f>
         <v>2258000</v>
       </c>
       <c r="B95" s="7"/>
@@ -2380,7 +2196,7 @@
     </row>
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B96" s="7"/>
@@ -2390,7 +2206,7 @@
     </row>
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B97" s="7"/>
@@ -2400,7 +2216,7 @@
     </row>
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B98" s="7"/>
@@ -2410,7 +2226,7 @@
     </row>
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B99" s="7"/>
@@ -2420,7 +2236,7 @@
     </row>
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B100" s="7"/>
@@ -2430,7 +2246,7 @@
     </row>
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B101" s="7"/>
@@ -2440,7 +2256,7 @@
     </row>
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B102" s="7"/>
@@ -2450,7 +2266,7 @@
     </row>
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B103" s="7"/>
@@ -2460,7 +2276,7 @@
     </row>
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B104" s="7"/>
@@ -2470,7 +2286,7 @@
     </row>
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B105" s="7"/>
@@ -2480,7 +2296,7 @@
     </row>
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B106" s="7"/>
@@ -2490,7 +2306,7 @@
     </row>
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B107" s="7"/>
@@ -2500,7 +2316,7 @@
     </row>
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B108" s="7"/>
@@ -2510,7 +2326,7 @@
     </row>
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B109" s="7"/>
@@ -2520,7 +2336,7 @@
     </row>
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B110" s="7"/>
@@ -2530,7 +2346,7 @@
     </row>
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v>2258000</v>
       </c>
       <c r="B111" s="7"/>
@@ -2555,7 +2371,7 @@
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
-        <v>11452000</v>
+        <v>11119000</v>
       </c>
     </row>
     <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -388,6 +388,12 @@
   </si>
   <si>
     <t>زعفران</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>سیگار تخمه عطر</t>
   </si>
 </sst>
 </file>
@@ -897,7 +903,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -934,7 +940,7 @@
     </row>
     <row r="5" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
-        <f t="shared" ref="A5:A15" si="0" xml:space="preserve"> A4 + B5-C5</f>
+        <f t="shared" ref="A5:A14" si="0" xml:space="preserve"> A4 + B5-C5</f>
         <v>313000</v>
       </c>
       <c r="B5" s="7">
@@ -2167,17 +2173,23 @@
     <row r="93" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <f xml:space="preserve"> C89+B93-C93</f>
-        <v>2258000</v>
-      </c>
-      <c r="B93" s="7"/>
+        <v>3133000</v>
+      </c>
+      <c r="B93" s="7">
+        <v>875000</v>
+      </c>
       <c r="C93" s="7"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
+      <c r="D93" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <f xml:space="preserve"> A93 +B94-C94</f>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -2187,7 +2199,7 @@
     <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <f t="shared" ref="A95:A111" si="4" xml:space="preserve"> A94 +B95-C95</f>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -2197,7 +2209,7 @@
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2207,7 +2219,7 @@
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2217,7 +2229,7 @@
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2227,7 +2239,7 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2237,7 +2249,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2247,7 +2259,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2257,7 +2269,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2267,7 +2279,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2277,7 +2289,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2287,7 +2299,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2297,7 +2309,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2307,7 +2319,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2317,7 +2329,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2327,7 +2339,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2337,7 +2349,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2347,7 +2359,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2357,7 +2369,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2367,7 +2379,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>13710000</v>
+        <v>14585000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2378,7 +2390,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>2258000</v>
+        <v>3133000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -394,6 +394,9 @@
   </si>
   <si>
     <t>سیگار تخمه عطر</t>
+  </si>
+  <si>
+    <t>1405/06/04</t>
   </si>
 </sst>
 </file>
@@ -903,7 +906,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2189,17 +2192,23 @@
     <row r="94" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <f xml:space="preserve"> A93 +B94-C94</f>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B94" s="7"/>
-      <c r="C94" s="7"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+      <c r="C94" s="7">
+        <v>1633000</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <f t="shared" ref="A95:A111" si="4" xml:space="preserve"> A94 +B95-C95</f>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -2209,7 +2218,7 @@
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2219,7 +2228,7 @@
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2229,7 +2238,7 @@
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2239,7 +2248,7 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2249,7 +2258,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2259,7 +2268,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2269,7 +2278,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2279,7 +2288,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2289,7 +2298,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2299,7 +2308,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2309,7 +2318,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2319,7 +2328,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2329,7 +2338,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2339,7 +2348,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2349,7 +2358,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2359,7 +2368,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2369,7 +2378,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2383,14 +2392,14 @@
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
-        <v>11119000</v>
+        <v>12752000</v>
       </c>
     </row>
     <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>3133000</v>
+        <v>1500000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="128">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -397,6 +397,12 @@
   </si>
   <si>
     <t>1405/06/04</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیگار   </t>
   </si>
 </sst>
 </file>
@@ -906,7 +912,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,17 +2214,23 @@
     <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <f t="shared" ref="A95:A111" si="4" xml:space="preserve"> A94 +B95-C95</f>
-        <v>1500000</v>
-      </c>
-      <c r="B95" s="7"/>
+        <v>1760000</v>
+      </c>
+      <c r="B95" s="7">
+        <v>260000</v>
+      </c>
       <c r="C95" s="7"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -2228,7 +2240,7 @@
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2238,7 +2250,7 @@
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2248,7 +2260,7 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2258,7 +2270,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2268,7 +2280,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2278,7 +2290,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2288,7 +2300,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2298,7 +2310,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2308,7 +2320,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2318,7 +2330,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2328,7 +2340,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2338,7 +2350,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2348,7 +2360,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2358,7 +2370,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2368,7 +2380,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2378,7 +2390,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2388,7 +2400,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>14585000</v>
+        <v>14845000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2399,7 +2411,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1500000</v>
+        <v>1760000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -403,6 +403,12 @@
   </si>
   <si>
     <t xml:space="preserve">سیگار   </t>
+  </si>
+  <si>
+    <t>1405/06/10</t>
+  </si>
+  <si>
+    <t>سیگار</t>
   </si>
 </sst>
 </file>
@@ -912,7 +918,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2230,17 +2236,23 @@
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
-      </c>
-      <c r="B96" s="7"/>
+        <v>1900000</v>
+      </c>
+      <c r="B96" s="7">
+        <v>140000</v>
+      </c>
       <c r="C96" s="7"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
+      <c r="D96" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -2250,7 +2262,7 @@
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2260,7 +2272,7 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2270,7 +2282,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2280,7 +2292,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2290,7 +2302,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2300,7 +2312,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2310,7 +2322,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2320,7 +2332,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2330,7 +2342,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2340,7 +2352,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2350,7 +2362,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2360,7 +2372,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2370,7 +2382,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2380,7 +2392,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2390,7 +2402,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2400,7 +2412,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>14845000</v>
+        <v>14985000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2411,7 +2423,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1760000</v>
+        <v>1900000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="132">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -409,6 +409,12 @@
   </si>
   <si>
     <t>سیگار</t>
+  </si>
+  <si>
+    <t>1405/06/11</t>
+  </si>
+  <si>
+    <t>سیگار تخمه شکلات</t>
   </si>
 </sst>
 </file>
@@ -918,7 +924,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2252,17 +2258,23 @@
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
-      </c>
-      <c r="B97" s="7"/>
+        <v>2820000</v>
+      </c>
+      <c r="B97" s="7">
+        <v>920000</v>
+      </c>
       <c r="C97" s="7"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+      <c r="D97" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -2272,7 +2284,7 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2282,7 +2294,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2292,7 +2304,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2302,7 +2314,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2312,7 +2324,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2322,7 +2334,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2332,7 +2344,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2342,7 +2354,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2352,7 +2364,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2362,7 +2374,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2372,7 +2384,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2382,7 +2394,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2392,7 +2404,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2402,7 +2414,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2412,7 +2424,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>14985000</v>
+        <v>15905000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2423,7 +2435,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1900000</v>
+        <v>2820000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="133">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>سیگار تخمه شکلات</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
   </si>
 </sst>
 </file>
@@ -924,7 +927,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,17 +2277,23 @@
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
-      </c>
-      <c r="B98" s="7"/>
+        <v>3260000</v>
+      </c>
+      <c r="B98" s="7">
+        <v>440000</v>
+      </c>
       <c r="C98" s="7"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
+      <c r="D98" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -2294,7 +2303,7 @@
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -2304,7 +2313,7 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2314,7 +2323,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2324,7 +2333,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2334,7 +2343,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2344,7 +2353,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2354,7 +2363,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2364,7 +2373,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2374,7 +2383,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2384,7 +2393,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2394,7 +2403,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2404,7 +2413,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2414,7 +2423,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2424,7 +2433,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>15905000</v>
+        <v>16345000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2435,7 +2444,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>2820000</v>
+        <v>3260000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="136">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -418,6 +418,15 @@
   </si>
   <si>
     <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/17</t>
+  </si>
+  <si>
+    <t>سیگار ابمیوه</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
   </si>
 </sst>
 </file>
@@ -927,7 +936,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2293,27 +2302,39 @@
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
-      </c>
-      <c r="B99" s="7"/>
+        <v>3460000</v>
+      </c>
+      <c r="B99" s="7">
+        <v>200000</v>
+      </c>
       <c r="C99" s="7"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
+      <c r="D99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
-      </c>
-      <c r="B100" s="7"/>
+        <v>3730000</v>
+      </c>
+      <c r="B100" s="7">
+        <v>270000</v>
+      </c>
       <c r="C100" s="7"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
+      <c r="D100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -2323,7 +2344,7 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2333,7 +2354,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2343,7 +2364,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2353,7 +2374,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2363,7 +2384,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2373,7 +2394,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2383,7 +2404,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2393,7 +2414,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2403,7 +2424,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2413,7 +2434,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2423,7 +2444,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2433,7 +2454,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>16345000</v>
+        <v>16815000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2444,7 +2465,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>3260000</v>
+        <v>3730000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="137">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -427,6 +427,9 @@
   </si>
   <si>
     <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>1405/06/19</t>
   </si>
 </sst>
 </file>
@@ -936,7 +939,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2334,17 +2337,23 @@
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
-      </c>
-      <c r="B101" s="7"/>
+        <v>4010000</v>
+      </c>
+      <c r="B101" s="7">
+        <v>280000</v>
+      </c>
       <c r="C101" s="7"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -2354,7 +2363,7 @@
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2364,7 +2373,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2374,7 +2383,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2384,7 +2393,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2394,7 +2403,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2404,7 +2413,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2414,7 +2423,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2424,7 +2433,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2434,7 +2443,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2444,7 +2453,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2454,7 +2463,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>16815000</v>
+        <v>17095000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2465,7 +2474,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>3730000</v>
+        <v>4010000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>

--- a/customers/morteza shamsi.xlsx
+++ b/customers/morteza shamsi.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="138">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>1405/06/19</t>
+  </si>
+  <si>
+    <t>1405/06/20</t>
   </si>
 </sst>
 </file>
@@ -939,7 +942,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2353,17 +2356,23 @@
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
-      </c>
-      <c r="B102" s="7"/>
+        <v>4490000</v>
+      </c>
+      <c r="B102" s="7">
+        <v>480000</v>
+      </c>
       <c r="C102" s="7"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -2373,7 +2382,7 @@
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -2383,7 +2392,7 @@
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -2393,7 +2402,7 @@
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -2403,7 +2412,7 @@
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -2413,7 +2422,7 @@
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -2423,7 +2432,7 @@
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -2433,7 +2442,7 @@
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -2443,7 +2452,7 @@
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -2453,7 +2462,7 @@
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2463,7 +2472,7 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>17095000</v>
+        <v>17575000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
@@ -2474,7 +2483,7 @@
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>4010000</v>
+        <v>4490000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>
